--- a/artfynd/A 7923-2025 artfynd.xlsx
+++ b/artfynd/A 7923-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,6 +1207,135 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122791937</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väsbyskogen, Fogdö bygdegård, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>605290</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6592929</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fogdö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växande på undersidan av granlåga liggandes i brant.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik de Joussineau</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik de Joussineau</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7923-2025 artfynd.xlsx
+++ b/artfynd/A 7923-2025 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7923-2025 artfynd.xlsx
+++ b/artfynd/A 7923-2025 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7923-2025 artfynd.xlsx
+++ b/artfynd/A 7923-2025 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7923-2025 artfynd.xlsx
+++ b/artfynd/A 7923-2025 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7923-2025 artfynd.xlsx
+++ b/artfynd/A 7923-2025 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7923-2025 artfynd.xlsx
+++ b/artfynd/A 7923-2025 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
